--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.04162592297215</v>
+        <v>9.269264212482975</v>
       </c>
       <c r="D2" t="n">
-        <v>54.39236394645104</v>
+        <v>8.838759141298295</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F2" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.11040071560226</v>
+        <v>7.492940116285368</v>
       </c>
       <c r="D3" t="n">
-        <v>45.90714310051738</v>
+        <v>7.459910753834075</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F3" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.97157095192004</v>
+        <v>1.945380279687007</v>
       </c>
       <c r="D4" t="n">
-        <v>11.7374601423592</v>
+        <v>1.907337273133369</v>
       </c>
       <c r="E4" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F4" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.76240620030054</v>
+        <v>4.023891007548838</v>
       </c>
       <c r="D5" t="n">
-        <v>4.011430889069108</v>
+        <v>0.6518575194737301</v>
       </c>
       <c r="E5" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F5" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.96227030136785</v>
+        <v>6.168868923972276</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83027873059902</v>
+        <v>6.147420293722341</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F6" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.29373650322368</v>
+        <v>8.985232181773849</v>
       </c>
       <c r="D7" t="n">
-        <v>27.50257402094898</v>
+        <v>4.46916827840421</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F7" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.27151607524489</v>
+        <v>1.994121362227296</v>
       </c>
       <c r="D8" t="n">
-        <v>12.47663728681279</v>
+        <v>2.027453559107079</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F8" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.06260312258554</v>
+        <v>7.32267300742015</v>
       </c>
       <c r="D9" t="n">
-        <v>44.7017896733453</v>
+        <v>7.264040821918611</v>
       </c>
       <c r="E9" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F9" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.06285236447344</v>
+        <v>6.510213509226934</v>
       </c>
       <c r="D10" t="n">
-        <v>39.70201506221063</v>
+        <v>6.451577447609228</v>
       </c>
       <c r="E10" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F10" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.50156802753436</v>
+        <v>6.906504804474334</v>
       </c>
       <c r="D11" t="n">
-        <v>40.16215147266061</v>
+        <v>6.52634961430735</v>
       </c>
       <c r="E11" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F11" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.44709163706802</v>
+        <v>5.110152391023553</v>
       </c>
       <c r="D12" t="n">
-        <v>31.62279872447201</v>
+        <v>5.138704792726702</v>
       </c>
       <c r="E12" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F12" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.825615454405473</v>
+        <v>0.9466625113408894</v>
       </c>
       <c r="D13" t="n">
-        <v>5.502473650724641</v>
+        <v>0.8941519682427542</v>
       </c>
       <c r="E13" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F13" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.32735272849502</v>
+        <v>2.00319481838044</v>
       </c>
       <c r="D14" t="n">
-        <v>12.5008957601465</v>
+        <v>2.031395561023806</v>
       </c>
       <c r="E14" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F14" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.18964377893621</v>
+        <v>7.505817114077134</v>
       </c>
       <c r="D15" t="n">
-        <v>46.34222987093369</v>
+        <v>7.530612354026724</v>
       </c>
       <c r="E15" t="n">
-        <v>16.55243083604666</v>
+        <v>2.689770010857583</v>
       </c>
       <c r="F15" t="n">
-        <v>16.51603890718525</v>
+        <v>2.683856322417604</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
